--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747943</v>
+        <v>122747946</v>
       </c>
       <c r="B2" t="n">
-        <v>79278</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717288</v>
+        <v>717357</v>
       </c>
       <c r="R2" t="n">
-        <v>7172817</v>
+        <v>7172808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747946</v>
+        <v>122747943</v>
       </c>
       <c r="B3" t="n">
-        <v>74761</v>
+        <v>79380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717357</v>
+        <v>717288</v>
       </c>
       <c r="R3" t="n">
-        <v>7172808</v>
+        <v>7172817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747942</v>
+        <v>122747941</v>
       </c>
       <c r="B4" t="n">
-        <v>78396</v>
+        <v>92221</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717286</v>
+        <v>717170</v>
       </c>
       <c r="R4" t="n">
-        <v>7172818</v>
+        <v>7172879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747940</v>
+        <v>122747945</v>
       </c>
       <c r="B5" t="n">
-        <v>77592</v>
+        <v>79380</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717176</v>
+        <v>717329</v>
       </c>
       <c r="R5" t="n">
-        <v>7172951</v>
+        <v>7172816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747941</v>
+        <v>122747944</v>
       </c>
       <c r="B6" t="n">
-        <v>92118</v>
+        <v>78498</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1111,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717170</v>
+        <v>717330</v>
       </c>
       <c r="R6" t="n">
-        <v>7172879</v>
+        <v>7172816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747945</v>
+        <v>122747942</v>
       </c>
       <c r="B7" t="n">
-        <v>79278</v>
+        <v>78498</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717329</v>
+        <v>717286</v>
       </c>
       <c r="R7" t="n">
-        <v>7172816</v>
+        <v>7172818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1314,7 @@
         <v>122747938</v>
       </c>
       <c r="B8" t="n">
-        <v>78044</v>
+        <v>78146</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747947</v>
+        <v>122747940</v>
       </c>
       <c r="B9" t="n">
-        <v>74761</v>
+        <v>77694</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717369</v>
+        <v>717176</v>
       </c>
       <c r="R9" t="n">
-        <v>7172813</v>
+        <v>7172951</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747944</v>
+        <v>122747947</v>
       </c>
       <c r="B10" t="n">
-        <v>78396</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717330</v>
+        <v>717369</v>
       </c>
       <c r="R10" t="n">
-        <v>7172816</v>
+        <v>7172813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747942</v>
+        <v>122747938</v>
       </c>
       <c r="B7" t="n">
-        <v>78498</v>
+        <v>78146</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717286</v>
+        <v>717178</v>
       </c>
       <c r="R7" t="n">
-        <v>7172818</v>
+        <v>7172949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747938</v>
+        <v>122747942</v>
       </c>
       <c r="B8" t="n">
-        <v>78146</v>
+        <v>78498</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717178</v>
+        <v>717286</v>
       </c>
       <c r="R8" t="n">
-        <v>7172949</v>
+        <v>7172818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747946</v>
+        <v>122747942</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717357</v>
+        <v>717286</v>
       </c>
       <c r="R2" t="n">
-        <v>7172808</v>
+        <v>7172818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747943</v>
+        <v>122747941</v>
       </c>
       <c r="B3" t="n">
-        <v>79380</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717288</v>
+        <v>717170</v>
       </c>
       <c r="R3" t="n">
-        <v>7172817</v>
+        <v>7172879</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747941</v>
+        <v>122747943</v>
       </c>
       <c r="B4" t="n">
-        <v>92221</v>
+        <v>79384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717170</v>
+        <v>717288</v>
       </c>
       <c r="R4" t="n">
-        <v>7172879</v>
+        <v>7172817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747945</v>
+        <v>122747940</v>
       </c>
       <c r="B5" t="n">
-        <v>79380</v>
+        <v>77694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717329</v>
+        <v>717176</v>
       </c>
       <c r="R5" t="n">
-        <v>7172816</v>
+        <v>7172951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747944</v>
+        <v>122747945</v>
       </c>
       <c r="B6" t="n">
-        <v>78498</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717330</v>
+        <v>717329</v>
       </c>
       <c r="R6" t="n">
         <v>7172816</v>
@@ -1208,7 +1208,7 @@
         <v>122747938</v>
       </c>
       <c r="B7" t="n">
-        <v>78146</v>
+        <v>78150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747942</v>
+        <v>122747944</v>
       </c>
       <c r="B8" t="n">
-        <v>78498</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717286</v>
+        <v>717330</v>
       </c>
       <c r="R8" t="n">
-        <v>7172818</v>
+        <v>7172816</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747940</v>
+        <v>122747947</v>
       </c>
       <c r="B9" t="n">
-        <v>77694</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717176</v>
+        <v>717369</v>
       </c>
       <c r="R9" t="n">
-        <v>7172951</v>
+        <v>7172813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747947</v>
+        <v>122747946</v>
       </c>
       <c r="B10" t="n">
         <v>74863</v>
@@ -1559,14 +1559,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717369</v>
+        <v>717357</v>
       </c>
       <c r="R10" t="n">
-        <v>7172813</v>
+        <v>7172808</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747942</v>
+        <v>122747947</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717286</v>
+        <v>717369</v>
       </c>
       <c r="R2" t="n">
-        <v>7172818</v>
+        <v>7172813</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747941</v>
+        <v>122747940</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
+        <v>77694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717170</v>
+        <v>717176</v>
       </c>
       <c r="R3" t="n">
-        <v>7172879</v>
+        <v>7172951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747943</v>
+        <v>122747941</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717288</v>
+        <v>717170</v>
       </c>
       <c r="R4" t="n">
-        <v>7172817</v>
+        <v>7172879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747940</v>
+        <v>122747945</v>
       </c>
       <c r="B5" t="n">
-        <v>77694</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717176</v>
+        <v>717329</v>
       </c>
       <c r="R5" t="n">
-        <v>7172951</v>
+        <v>7172816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747945</v>
+        <v>122747938</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>78150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717329</v>
+        <v>717178</v>
       </c>
       <c r="R6" t="n">
-        <v>7172816</v>
+        <v>7172949</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747938</v>
+        <v>122747943</v>
       </c>
       <c r="B7" t="n">
-        <v>78150</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717178</v>
+        <v>717288</v>
       </c>
       <c r="R7" t="n">
-        <v>7172949</v>
+        <v>7172817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747947</v>
+        <v>122747942</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717369</v>
+        <v>717286</v>
       </c>
       <c r="R9" t="n">
-        <v>7172813</v>
+        <v>7172818</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747940</v>
+        <v>122747946</v>
       </c>
       <c r="B3" t="n">
-        <v>77694</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717176</v>
+        <v>717357</v>
       </c>
       <c r="R3" t="n">
-        <v>7172951</v>
+        <v>7172808</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747941</v>
+        <v>122747943</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>79384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +899,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717170</v>
+        <v>717288</v>
       </c>
       <c r="R4" t="n">
-        <v>7172879</v>
+        <v>7172817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747945</v>
+        <v>122747938</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>78150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717329</v>
+        <v>717178</v>
       </c>
       <c r="R5" t="n">
-        <v>7172816</v>
+        <v>7172949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747938</v>
+        <v>122747942</v>
       </c>
       <c r="B6" t="n">
-        <v>78150</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717178</v>
+        <v>717286</v>
       </c>
       <c r="R6" t="n">
-        <v>7172949</v>
+        <v>7172818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747943</v>
+        <v>122747945</v>
       </c>
       <c r="B7" t="n">
         <v>79384</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717288</v>
+        <v>717329</v>
       </c>
       <c r="R7" t="n">
-        <v>7172817</v>
+        <v>7172816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747944</v>
+        <v>122747941</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>92225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717330</v>
+        <v>717170</v>
       </c>
       <c r="R8" t="n">
-        <v>7172816</v>
+        <v>7172879</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747942</v>
+        <v>122747944</v>
       </c>
       <c r="B9" t="n">
         <v>78502</v>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717286</v>
+        <v>717330</v>
       </c>
       <c r="R9" t="n">
-        <v>7172818</v>
+        <v>7172816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747946</v>
+        <v>122747940</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>77694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717357</v>
+        <v>717176</v>
       </c>
       <c r="R10" t="n">
-        <v>7172808</v>
+        <v>7172951</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747947</v>
+        <v>122747942</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717369</v>
+        <v>717286</v>
       </c>
       <c r="R2" t="n">
-        <v>7172813</v>
+        <v>7172818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747946</v>
+        <v>122747940</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>77694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717357</v>
+        <v>717176</v>
       </c>
       <c r="R3" t="n">
-        <v>7172808</v>
+        <v>7172951</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747943</v>
+        <v>122747938</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
+        <v>78150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717288</v>
+        <v>717178</v>
       </c>
       <c r="R4" t="n">
-        <v>7172817</v>
+        <v>7172949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747938</v>
+        <v>122747941</v>
       </c>
       <c r="B5" t="n">
-        <v>78150</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717178</v>
+        <v>717170</v>
       </c>
       <c r="R5" t="n">
-        <v>7172949</v>
+        <v>7172879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747942</v>
+        <v>122747944</v>
       </c>
       <c r="B6" t="n">
         <v>78502</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717286</v>
+        <v>717330</v>
       </c>
       <c r="R6" t="n">
-        <v>7172818</v>
+        <v>7172816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747945</v>
+        <v>122747943</v>
       </c>
       <c r="B7" t="n">
         <v>79384</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717329</v>
+        <v>717288</v>
       </c>
       <c r="R7" t="n">
-        <v>7172816</v>
+        <v>7172817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747941</v>
+        <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>92225</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,38 +1323,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717170</v>
+        <v>717357</v>
       </c>
       <c r="R8" t="n">
-        <v>7172879</v>
+        <v>7172808</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747944</v>
+        <v>122747947</v>
       </c>
       <c r="B9" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717330</v>
+        <v>717369</v>
       </c>
       <c r="R9" t="n">
-        <v>7172816</v>
+        <v>7172813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747940</v>
+        <v>122747945</v>
       </c>
       <c r="B10" t="n">
-        <v>77694</v>
+        <v>79384</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717176</v>
+        <v>717329</v>
       </c>
       <c r="R10" t="n">
-        <v>7172951</v>
+        <v>7172816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747942</v>
+        <v>122747946</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717286</v>
+        <v>717357</v>
       </c>
       <c r="R2" t="n">
-        <v>7172818</v>
+        <v>7172808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747940</v>
+        <v>122747947</v>
       </c>
       <c r="B3" t="n">
-        <v>77694</v>
+        <v>74863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717176</v>
+        <v>717369</v>
       </c>
       <c r="R3" t="n">
-        <v>7172951</v>
+        <v>7172813</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747938</v>
+        <v>122747945</v>
       </c>
       <c r="B4" t="n">
-        <v>78150</v>
+        <v>79384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717178</v>
+        <v>717329</v>
       </c>
       <c r="R4" t="n">
-        <v>7172949</v>
+        <v>7172816</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747941</v>
+        <v>122747943</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1005,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717170</v>
+        <v>717288</v>
       </c>
       <c r="R5" t="n">
-        <v>7172879</v>
+        <v>7172817</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747943</v>
+        <v>122747938</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>78150</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717288</v>
+        <v>717178</v>
       </c>
       <c r="R7" t="n">
-        <v>7172817</v>
+        <v>7172949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747946</v>
+        <v>122747942</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717357</v>
+        <v>717286</v>
       </c>
       <c r="R8" t="n">
-        <v>7172808</v>
+        <v>7172818</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747947</v>
+        <v>122747940</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>77694</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717369</v>
+        <v>717176</v>
       </c>
       <c r="R9" t="n">
-        <v>7172813</v>
+        <v>7172951</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747945</v>
+        <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>79384</v>
+        <v>92233</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717329</v>
+        <v>717170</v>
       </c>
       <c r="R10" t="n">
-        <v>7172816</v>
+        <v>7172879</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747946</v>
+        <v>122747942</v>
       </c>
       <c r="B2" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717357</v>
+        <v>717286</v>
       </c>
       <c r="R2" t="n">
-        <v>7172808</v>
+        <v>7172818</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747947</v>
+        <v>122747941</v>
       </c>
       <c r="B3" t="n">
-        <v>74863</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717369</v>
+        <v>717170</v>
       </c>
       <c r="R3" t="n">
-        <v>7172813</v>
+        <v>7172879</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747945</v>
+        <v>122747938</v>
       </c>
       <c r="B4" t="n">
-        <v>79384</v>
+        <v>78150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717329</v>
+        <v>717178</v>
       </c>
       <c r="R4" t="n">
-        <v>7172816</v>
+        <v>7172949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747943</v>
+        <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>78502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717288</v>
+        <v>717330</v>
       </c>
       <c r="R5" t="n">
-        <v>7172817</v>
+        <v>7172816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747944</v>
+        <v>122747943</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>79384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717330</v>
+        <v>717288</v>
       </c>
       <c r="R6" t="n">
-        <v>7172816</v>
+        <v>7172817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747938</v>
+        <v>122747945</v>
       </c>
       <c r="B7" t="n">
-        <v>78150</v>
+        <v>79384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717178</v>
+        <v>717329</v>
       </c>
       <c r="R7" t="n">
-        <v>7172949</v>
+        <v>7172816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747942</v>
+        <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,21 +1327,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717286</v>
+        <v>717357</v>
       </c>
       <c r="R8" t="n">
-        <v>7172818</v>
+        <v>7172808</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747940</v>
+        <v>122747947</v>
       </c>
       <c r="B9" t="n">
-        <v>77694</v>
+        <v>74863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717176</v>
+        <v>717369</v>
       </c>
       <c r="R9" t="n">
-        <v>7172951</v>
+        <v>7172813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747941</v>
+        <v>122747940</v>
       </c>
       <c r="B10" t="n">
-        <v>92233</v>
+        <v>77694</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,25 +1535,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717170</v>
+        <v>717176</v>
       </c>
       <c r="R10" t="n">
-        <v>7172879</v>
+        <v>7172951</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747946</v>
+        <v>122747940</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>77694</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717357</v>
+        <v>717176</v>
       </c>
       <c r="R8" t="n">
-        <v>7172808</v>
+        <v>7172951</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747947</v>
+        <v>122747946</v>
       </c>
       <c r="B9" t="n">
         <v>74863</v>
@@ -1453,14 +1453,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717369</v>
+        <v>717357</v>
       </c>
       <c r="R9" t="n">
-        <v>7172813</v>
+        <v>7172808</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747940</v>
+        <v>122747947</v>
       </c>
       <c r="B10" t="n">
-        <v>77694</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717176</v>
+        <v>717369</v>
       </c>
       <c r="R10" t="n">
-        <v>7172951</v>
+        <v>7172813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747942</v>
+        <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>78502</v>
+        <v>79384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717286</v>
+        <v>717288</v>
       </c>
       <c r="R2" t="n">
-        <v>7172818</v>
+        <v>7172817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747941</v>
+        <v>122747945</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>79384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717170</v>
+        <v>717329</v>
       </c>
       <c r="R3" t="n">
-        <v>7172879</v>
+        <v>7172816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747938</v>
+        <v>122747941</v>
       </c>
       <c r="B4" t="n">
-        <v>78150</v>
+        <v>92233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717178</v>
+        <v>717170</v>
       </c>
       <c r="R4" t="n">
-        <v>7172949</v>
+        <v>7172879</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747944</v>
+        <v>122747940</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
+        <v>77694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717330</v>
+        <v>717176</v>
       </c>
       <c r="R5" t="n">
-        <v>7172816</v>
+        <v>7172951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747943</v>
+        <v>122747942</v>
       </c>
       <c r="B6" t="n">
-        <v>79384</v>
+        <v>78502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717288</v>
+        <v>717286</v>
       </c>
       <c r="R6" t="n">
-        <v>7172817</v>
+        <v>7172818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747945</v>
+        <v>122747946</v>
       </c>
       <c r="B7" t="n">
-        <v>79384</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717329</v>
+        <v>717357</v>
       </c>
       <c r="R7" t="n">
-        <v>7172816</v>
+        <v>7172808</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747940</v>
+        <v>122747947</v>
       </c>
       <c r="B8" t="n">
-        <v>77694</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,34 +1327,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717176</v>
+        <v>717369</v>
       </c>
       <c r="R8" t="n">
-        <v>7172951</v>
+        <v>7172813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747946</v>
+        <v>122747944</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717357</v>
+        <v>717330</v>
       </c>
       <c r="R9" t="n">
-        <v>7172808</v>
+        <v>7172816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747947</v>
+        <v>122747938</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>78150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717369</v>
+        <v>717178</v>
       </c>
       <c r="R10" t="n">
-        <v>7172813</v>
+        <v>7172949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747943</v>
+        <v>122747945</v>
       </c>
       <c r="B2" t="n">
         <v>79384</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717288</v>
+        <v>717329</v>
       </c>
       <c r="R2" t="n">
-        <v>7172817</v>
+        <v>7172816</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747945</v>
+        <v>122747944</v>
       </c>
       <c r="B3" t="n">
-        <v>79384</v>
+        <v>78502</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717329</v>
+        <v>717330</v>
       </c>
       <c r="R3" t="n">
         <v>7172816</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747940</v>
+        <v>122747938</v>
       </c>
       <c r="B5" t="n">
-        <v>77694</v>
+        <v>78150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717176</v>
+        <v>717178</v>
       </c>
       <c r="R5" t="n">
-        <v>7172951</v>
+        <v>7172949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747942</v>
+        <v>122747940</v>
       </c>
       <c r="B6" t="n">
-        <v>78502</v>
+        <v>77694</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717286</v>
+        <v>717176</v>
       </c>
       <c r="R6" t="n">
-        <v>7172818</v>
+        <v>7172951</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747946</v>
+        <v>122747942</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717357</v>
+        <v>717286</v>
       </c>
       <c r="R7" t="n">
-        <v>7172808</v>
+        <v>7172818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747947</v>
+        <v>122747946</v>
       </c>
       <c r="B8" t="n">
         <v>74863</v>
@@ -1347,14 +1347,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717369</v>
+        <v>717357</v>
       </c>
       <c r="R8" t="n">
-        <v>7172813</v>
+        <v>7172808</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747944</v>
+        <v>122747943</v>
       </c>
       <c r="B9" t="n">
-        <v>78502</v>
+        <v>79384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,21 +1433,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717330</v>
+        <v>717288</v>
       </c>
       <c r="R9" t="n">
-        <v>7172816</v>
+        <v>7172817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747938</v>
+        <v>122747947</v>
       </c>
       <c r="B10" t="n">
-        <v>78150</v>
+        <v>74863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717178</v>
+        <v>717369</v>
       </c>
       <c r="R10" t="n">
-        <v>7172949</v>
+        <v>7172813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747945</v>
+        <v>122747946</v>
       </c>
       <c r="B2" t="n">
-        <v>79384</v>
+        <v>74866</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717329</v>
+        <v>717357</v>
       </c>
       <c r="R2" t="n">
-        <v>7172816</v>
+        <v>7172808</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747944</v>
+        <v>122747943</v>
       </c>
       <c r="B3" t="n">
-        <v>78502</v>
+        <v>79387</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717330</v>
+        <v>717288</v>
       </c>
       <c r="R3" t="n">
-        <v>7172816</v>
+        <v>7172817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747941</v>
+        <v>122747938</v>
       </c>
       <c r="B4" t="n">
-        <v>92233</v>
+        <v>78153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717170</v>
+        <v>717178</v>
       </c>
       <c r="R4" t="n">
-        <v>7172879</v>
+        <v>7172949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747938</v>
+        <v>122747941</v>
       </c>
       <c r="B5" t="n">
-        <v>78150</v>
+        <v>92236</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717178</v>
+        <v>717170</v>
       </c>
       <c r="R5" t="n">
-        <v>7172949</v>
+        <v>7172879</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747940</v>
+        <v>122747942</v>
       </c>
       <c r="B6" t="n">
-        <v>77694</v>
+        <v>78505</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717176</v>
+        <v>717286</v>
       </c>
       <c r="R6" t="n">
-        <v>7172951</v>
+        <v>7172818</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747942</v>
+        <v>122747944</v>
       </c>
       <c r="B7" t="n">
-        <v>78502</v>
+        <v>78505</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717286</v>
+        <v>717330</v>
       </c>
       <c r="R7" t="n">
-        <v>7172818</v>
+        <v>7172816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747946</v>
+        <v>122747947</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,14 +1347,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717357</v>
+        <v>717369</v>
       </c>
       <c r="R8" t="n">
-        <v>7172808</v>
+        <v>7172813</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747943</v>
+        <v>122747940</v>
       </c>
       <c r="B9" t="n">
-        <v>79384</v>
+        <v>77697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717288</v>
+        <v>717176</v>
       </c>
       <c r="R9" t="n">
-        <v>7172817</v>
+        <v>7172951</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747947</v>
+        <v>122747945</v>
       </c>
       <c r="B10" t="n">
-        <v>74863</v>
+        <v>79387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717369</v>
+        <v>717329</v>
       </c>
       <c r="R10" t="n">
-        <v>7172813</v>
+        <v>7172816</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122747946</v>
+        <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>74866</v>
+        <v>79389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717357</v>
+        <v>717288</v>
       </c>
       <c r="R2" t="n">
-        <v>7172808</v>
+        <v>7172817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747943</v>
+        <v>122747938</v>
       </c>
       <c r="B3" t="n">
-        <v>79387</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717288</v>
+        <v>717178</v>
       </c>
       <c r="R3" t="n">
-        <v>7172817</v>
+        <v>7172949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747938</v>
+        <v>122747942</v>
       </c>
       <c r="B4" t="n">
-        <v>78153</v>
+        <v>78507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717178</v>
+        <v>717286</v>
       </c>
       <c r="R4" t="n">
-        <v>7172949</v>
+        <v>7172818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747941</v>
+        <v>122747940</v>
       </c>
       <c r="B5" t="n">
-        <v>92236</v>
+        <v>77699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717170</v>
+        <v>717176</v>
       </c>
       <c r="R5" t="n">
-        <v>7172879</v>
+        <v>7172951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747942</v>
+        <v>122747944</v>
       </c>
       <c r="B6" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717286</v>
+        <v>717330</v>
       </c>
       <c r="R6" t="n">
-        <v>7172818</v>
+        <v>7172816</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747944</v>
+        <v>122747947</v>
       </c>
       <c r="B7" t="n">
-        <v>78505</v>
+        <v>74866</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717330</v>
+        <v>717369</v>
       </c>
       <c r="R7" t="n">
-        <v>7172816</v>
+        <v>7172813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122747947</v>
+        <v>122747946</v>
       </c>
       <c r="B8" t="n">
         <v>74866</v>
@@ -1347,14 +1347,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717369</v>
+        <v>717357</v>
       </c>
       <c r="R8" t="n">
-        <v>7172813</v>
+        <v>7172808</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122747940</v>
+        <v>122747945</v>
       </c>
       <c r="B9" t="n">
-        <v>77697</v>
+        <v>79389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,34 +1433,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717176</v>
+        <v>717329</v>
       </c>
       <c r="R9" t="n">
-        <v>7172951</v>
+        <v>7172816</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122747945</v>
+        <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>79387</v>
+        <v>92238</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717329</v>
+        <v>717170</v>
       </c>
       <c r="R10" t="n">
-        <v>7172816</v>
+        <v>7172879</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747940</v>
+        <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>77699</v>
+        <v>78507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,34 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bräntkläppen S, Vb</t>
+          <t>Bräntkläppen SV, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717176</v>
+        <v>717330</v>
       </c>
       <c r="R5" t="n">
-        <v>7172951</v>
+        <v>7172816</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122747944</v>
+        <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
+        <v>74866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,34 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntkläppen SV, Vb</t>
+          <t>Bräntkläppen NV, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717330</v>
+        <v>717369</v>
       </c>
       <c r="R6" t="n">
-        <v>7172816</v>
+        <v>7172813</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122747947</v>
+        <v>122747940</v>
       </c>
       <c r="B7" t="n">
-        <v>74866</v>
+        <v>77699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntkläppen NV, Vb</t>
+          <t>Bräntkläppen S, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717369</v>
+        <v>717176</v>
       </c>
       <c r="R7" t="n">
-        <v>7172813</v>
+        <v>7172951</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747938</v>
       </c>
       <c r="B3" t="n">
-        <v>78718</v>
+        <v>78720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122747942</v>
       </c>
       <c r="B4" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747940</v>
       </c>
       <c r="B7" t="n">
-        <v>78322</v>
+        <v>78324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>83295</v>
+        <v>83297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>122747945</v>
       </c>
       <c r="B9" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747938</v>
       </c>
       <c r="B3" t="n">
-        <v>78720</v>
+        <v>78722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122747942</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747940</v>
       </c>
       <c r="B7" t="n">
-        <v>78324</v>
+        <v>78326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>83297</v>
+        <v>83299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>122747945</v>
       </c>
       <c r="B9" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747938</v>
       </c>
       <c r="B3" t="n">
-        <v>78722</v>
+        <v>78730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122747942</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747940</v>
       </c>
       <c r="B7" t="n">
-        <v>78326</v>
+        <v>78334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>83299</v>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>122747945</v>
       </c>
       <c r="B9" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747938</v>
       </c>
       <c r="B3" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122747942</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747940</v>
       </c>
       <c r="B7" t="n">
-        <v>78334</v>
+        <v>78335</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>83307</v>
+        <v>83308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>122747945</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>79947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -1082,7 +1082,7 @@
         <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>83308</v>
+        <v>83310</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 47105-2024 artfynd.xlsx
+++ b/artfynd/A 47105-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122747943</v>
       </c>
       <c r="B2" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>122747938</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>122747942</v>
       </c>
       <c r="B4" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>122747944</v>
       </c>
       <c r="B5" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>122747947</v>
       </c>
       <c r="B6" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>122747940</v>
       </c>
       <c r="B7" t="n">
-        <v>78335</v>
+        <v>78336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>122747946</v>
       </c>
       <c r="B8" t="n">
-        <v>83310</v>
+        <v>83311</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>122747945</v>
       </c>
       <c r="B9" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>122747941</v>
       </c>
       <c r="B10" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
